--- a/engine/adapters/outbound/excel/templates/Financial Model Template.xlsx
+++ b/engine/adapters/outbound/excel/templates/Financial Model Template.xlsx
@@ -121,13 +121,13 @@
     <t>Customer Pays</t>
   </si>
   <si>
-    <t>Celfocus Profit (Margin)</t>
+    <t>RB Profit (Margin)</t>
   </si>
   <si>
     <t>Customer Funded Cost</t>
   </si>
   <si>
-    <t>Celfocus Cost Contribution</t>
+    <t>RB Cost Contribution</t>
   </si>
   <si>
     <t>S1) Full Customer Funding</t>
